--- a/appointments-data.xlsx
+++ b/appointments-data.xlsx
@@ -457,25 +457,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>APT-1780050814424</v>
+        <v>APT-1780107703</v>
       </c>
       <c r="B2" t="str">
-        <v>100001</v>
+        <v>100016</v>
       </c>
       <c r="C2" t="str">
-        <v>Krrish Bagaria</v>
+        <v>Aditya Malhotra</v>
       </c>
       <c r="D2" t="str">
-        <v>9819815966</v>
+        <v>9844556677</v>
       </c>
       <c r="E2" t="str">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="F2" s="1" t="d">
-        <v>2026-05-30T00:00:00.000Z</v>
+        <v>2026-06-01T00:00:00.000Z</v>
       </c>
       <c r="G2" t="str">
-        <v>7:05 PM</v>
+        <v>12:00 PM</v>
       </c>
     </row>
   </sheetData>
@@ -487,7 +487,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -538,15 +538,84 @@
         <v>45</v>
       </c>
       <c r="F2" s="1" t="d">
-        <v>2026-05-23T00:00:00.000Z</v>
+        <v>2026-05-22T00:00:00.000Z</v>
       </c>
       <c r="G2" t="str">
         <v>12:00 PM</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>APT-1780109768927</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>Priya Kumari</v>
+      </c>
+      <c r="D3" t="str">
+        <v>9819817556</v>
+      </c>
+      <c r="E3" t="str">
+        <v>32</v>
+      </c>
+      <c r="F3" s="1" t="d">
+        <v>2026-05-30T00:00:00.000Z</v>
+      </c>
+      <c r="G3" t="str">
+        <v>12:00 PM</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>APT-1780107698</v>
+      </c>
+      <c r="B4" t="str">
+        <v>100011</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Kavya Nair</v>
+      </c>
+      <c r="D4" t="str">
+        <v>9877001122</v>
+      </c>
+      <c r="E4" t="str">
+        <v>29</v>
+      </c>
+      <c r="F4" s="1" t="d">
+        <v>2026-05-30T00:00:00.000Z</v>
+      </c>
+      <c r="G4" t="str">
+        <v>12:55 PM</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>APT-1780107702</v>
+      </c>
+      <c r="B5" t="str">
+        <v>100015</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Meera Kulkarni</v>
+      </c>
+      <c r="D5" t="str">
+        <v>9888776655</v>
+      </c>
+      <c r="E5" t="str">
+        <v>27</v>
+      </c>
+      <c r="F5" s="1" t="d">
+        <v>2026-05-31T00:00:00.000Z</v>
+      </c>
+      <c r="G5" t="str">
+        <v>12:25 PM</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
   </ignoredErrors>
 </worksheet>
 </file>